--- a/Heineken_failed_to_download.xlsx
+++ b/Heineken_failed_to_download.xlsx
@@ -441,8 +441,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
-        <v>28598489</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>28598489</t>
+        </is>
       </c>
     </row>
   </sheetData>
